--- a/spectakeoff/RCCD_Closeout_Schedule.xlsx
+++ b/spectakeoff/RCCD_Closeout_Schedule.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source: RCCD.pdf (509 pages) - 78 requirements. Every quote verified word-for-word against the cited page.</t>
+          <t>Source: RCCD.pdf (509 pages) - 75 requirements. Every quote verified word-for-word against the cited page.</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>01 40 00</t>
+          <t>01 70 00</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>QUALITY REQUIREMENTS</t>
+          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -880,18 +880,18 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>When specified in individual specification sections, require material or product suppliers or manufacturers to</t>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>When specified in individual specification sections, require material or product suppliers or manufacturers to provide qualified staff personnel to observe site conditions, conditions of surfaces and installation, quality of workmanship, start-up of equipment,test, adjust and balance of equipmentand operation as applicable, and to initiate instructions when necessary.</t>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+          <t>qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's pe</t>
         </is>
       </c>
       <c r="E10" s="4" t="n"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
+          <t>Provide a qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's personnel.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -955,50 +955,56 @@
       <c r="N10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's pe</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="n">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>8 hours minimum of demonstration and training</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Provide a qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's personnel.</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Provide 8 hours minimum of demonstration and training.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1013,33 +1019,29 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>8 hours minimum of demonstration and training</t>
+          <t>bound hardcopies - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Provide 8 hours minimum of demonstration and training.</t>
+          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1070,7 +1072,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>bound hardcopies - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
+          <t>archival-grade (gold foil) DVDs - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
@@ -1101,108 +1103,108 @@
       <c r="N13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Period</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>from the Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Period: As indicated in specification sections or, if not indicated, not less than one year from the Date of Substantial Completion or the length of the specified warranty, whichever is longer.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>01 78 00</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEOUT SUBMITTALS</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>archival-grade (gold foil) DVDs - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>two sets of revised final documents in final form within 10 days after final inspection</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Submit two sets of revised final documents in final form within 10 days after final inspection.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>01 70 00</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Period</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>from the Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Period: As indicated in specification sections or, if not indicated, not less than one year from the Date of Substantial Completion or the length of the specified warranty, whichever is longer.</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1222,7 +1224,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>two sets of revised final documents in final form within 10 days after final inspection</t>
+          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -1230,7 +1232,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -1239,7 +1241,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Submit two sets of revised final documents in final form within 10 days after final inspection.</t>
+          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1270,24 +1272,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
+          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
+          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1318,24 +1320,24 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+          <t>warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, withi</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+          <t>Obtain warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, within 10 days after completion of the applicable item of work.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1349,52 +1351,60 @@
       <c r="N18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>01 78 00</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>CLOSEOUT SUBMITTALS</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>01 79 00</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>DEMONSTRATION AND TRAINING</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, withi</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Training Manuals</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Obtain warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, within 10 days after completion of the applicable item of work.</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>for each attendee</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>257</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Training Manuals: Provide training manual for each attendee; allow for minimum of two attendees per training session.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1414,7 +1424,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Training Manuals</t>
+          <t>one extra copy of each training manual to be included with operation and maintenance data</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1427,7 +1437,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>for each attendee</t>
+          <t>of each training manual to be included with operation and maintenance data</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
@@ -1435,7 +1445,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Training Manuals: Provide training manual for each attendee; allow for minimum of two attendees per training session.</t>
+          <t>Provide one extra copy of each training manual to be included with operation and maintenance data.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1465,33 +1475,23 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>one extra copy of each training manual to be included with operation and maintenance data</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>of each training manual to be included with operation and maintenance data</t>
-        </is>
-      </c>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Provide one extra copy of each training manual to be included with operation and maintenance data.</t>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L21" s="4" t="n"/>
@@ -1509,91 +1509,93 @@
       <c r="N21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="n">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>8 hours of training</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Provide minimum 8 hours of training.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>03 30 00</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>DEMONSTRATION AND TRAINING</t>
+          <t>CAST IN PLACE CONCRETE</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>8 hours of training</t>
+          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA)</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="n">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum 8 hours of training.</t>
+          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA): Provide warranty to cover the cost of flooring failures due to moisture migration from slabs for ten years.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1607,133 +1609,137 @@
       <c r="N23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Training schedule will be subject to availability of Owner's personnel to be trained; re-schedule training ses</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="n">
-        <v>258</v>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Training schedule will be subject to availability of Owner's personnel to be trained; re-schedule training sessions as required by Owner; once schedule has been approved by Owner failure to conduct sessions according to schedule will be cause for Owner to charge Contractor for personnel "show-up" time.</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>03 30 00</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>CAST IN PLACE CONCRETE</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Moisture Emission Reducing Curing and Sealing Compound</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Moisture Emission Reducing Curing and Sealing Compound: Provide warranty to cost of flooring delamination failures for 10 years.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Be prepared to answer questions raised by training attendees; if unable to answer during training session, pro</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Be prepared to answer questions raised by training attendees; if unable to answer during training session, provide written response within three days.</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: 3 day(s) stated - hours per day not stated in spec</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>09 51 00</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>ACOUSTICAL CEILINGS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Provide 100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>03 30 00</t>
+          <t>09 51 00</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CAST IN PLACE CONCRETE</t>
+          <t>ACOUSTICAL CEILINGS</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Attic Stock</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA)</t>
+          <t>1 box of Type A2 acoustical unit, for Owner's use in maintenance of project</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="n">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA): Provide warranty to cover the cost of flooring failures due to moisture migration from slabs for ten years.</t>
+          <t>Provide 1 box of Type A2 acoustical unit, for Owner's use in maintenance of project.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1747,89 +1753,97 @@
       <c r="N26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>03 30 00</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>CAST IN PLACE CONCRETE</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Moisture Emission Reducing Curing and Sealing Compound</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Moisture Emission Reducing Curing and Sealing Compound: Provide warranty to cost of flooring delamination failures for 10 years.</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>09 90 00</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>PAINTS AND COATINGS</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>1 gallon of each color; store where directed</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>GAL</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>of each color</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Supply 1 gallon of each color; store where directed.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>09 51 00</t>
+          <t>23 05 13</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ACOUSTICAL CEILINGS</t>
+          <t>MOTOR REQUIREMENTS FOR HVAC AND PLUMBING EQUIPMENT</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project</t>
+          <t>five year manufacturer warranty for motors larger than 20 horsepower</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Provide 100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project.</t>
+          <t>Provide five year manufacturer warranty for motors larger than 20 horsepower.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1843,243 +1857,243 @@
       <c r="N28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>09 51 00</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>ACOUSTICAL CEILINGS</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>1 box of Type A2 acoustical unit, for Owner's use in maintenance of project</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Provide 1 box of Type A2 acoustical unit, for Owner's use in maintenance of project.</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>23 05 16</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>EXPANSION FITTINGS AND LOOPS FOR HVAC PIPING</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>two sets of packing for each packed expansion joint</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>for each packed expansion joint</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Supply two sets of packing for each packed expansion joint.</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>23 05 93</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>TESTING, ADJUSTING, AND BALANCING FOR HVAC</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>final copies for Architect and for inclusion in operating and maintenance manuals</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="n">
+        <v>326</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Provide final copies for Architect and for inclusion in operating and maintenance manuals.</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>09 90 00</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>PAINTS AND COATINGS</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>1 gallon of each color; store where directed</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>GAL</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>of each color</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>296</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Supply 1 gallon of each color; store where directed.</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>23 09 13</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>INSTRUMENTATION AND CONTROL DEVICES FOR HVAC</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>352</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Provide service and maintenance of control system for two years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>23 05 13</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>MOTOR REQUIREMENTS FOR HVAC AND PLUMBING EQUIPMENT</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>23 09 23</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Extended Warranty</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>five year manufacturer warranty for motors larger than 20 horsepower</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>defective Work within a five year period after Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="n">
-        <v>301</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Provide five year manufacturer warranty for motors larger than 20 horsepower.</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="n">
+        <v>354</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Correct defective Work within a five year period after Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>23 05 16</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>EXPANSION FITTINGS AND LOOPS FOR HVAC PIPING</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>two sets of packing for each packed expansion joint</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>for each packed expansion joint</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>309</v>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Supply two sets of packing for each packed expansion joint.</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>23 05 93</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>TESTING, ADJUSTING, AND BALANCING FOR HVAC</t>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>final copies for Architect and for inclusion in operating and maintenance manuals</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="inlineStr"/>
+          <t>five year manufacturer's warranty for field programmable micro-processor based units</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="n">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Provide final copies for Architect and for inclusion in operating and maintenance manuals.</t>
+          <t>Provide five year manufacturer's warranty for field programmable micro-processor based units.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2095,12 +2109,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>23 09 13</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION AND CONTROL DEVICES FOR HVAC</t>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2110,11 +2124,11 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
+          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -2127,11 +2141,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Provide service and maintenance of control system for two years from Date of Substantial Completion.</t>
+          <t>Provide service and maintenance of energy management and control systems for one years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2149,52 +2163,60 @@
       <c r="N34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>23 09 23</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>defective Work within a five year period after Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="n">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
         <v>354</v>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>Correct defective Work within a five year period after Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Provide four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required, and submit written reports.</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2209,29 +2231,33 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>five year manufacturer's warranty for field programmable micro-processor based units</t>
+          <t xml:space="preserve">Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service </t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr"/>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H36" s="3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Provide five year manufacturer's warranty for field programmable micro-processor based units.</t>
+          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service calls to inspect, calibrate, and adjust controls, and submit written reports.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2257,33 +2283,29 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
+          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Provide service and maintenance of energy management and control systems for one years from Date of Substantial Completion.</t>
+          <t>Provide service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day period.</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2293,7 +2315,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
       <c r="L37" s="4" t="n"/>
@@ -2301,149 +2323,153 @@
       <c r="N37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>23 09 23</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>minimum of 8 hours dedicated instructor time</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Include a minimum of 8 hours dedicated instructor time.</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>23 21 13</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>HYDRONIC PIPING</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Special Tool</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>per year</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>354</v>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Provide four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required, and submit written reports.</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>for every ten plug valves minimum of one</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Operator: One plug valve wrench for every ten plug valves minimum of one.</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>23 09 23</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service </t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>355</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service calls to inspect, calibrate, and adjust controls, and submit written reports.</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 21 23</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+          <t>HYDRONIC PUMPS</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
+          <t>Extra Pump Seals</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>DAY</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>for each type and size of pump</t>
+        </is>
+      </c>
       <c r="H40" s="4" t="n">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Provide service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day period.</t>
+          <t>Extra Pump Seals: One set for each type and size of pump.</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2453,7 +2479,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L40" s="4" t="n"/>
@@ -2461,97 +2487,95 @@
       <c r="N40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>23 09 23</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>minimum of 8 hours dedicated instructor time</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>373</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Include a minimum of 8 hours dedicated instructor time.</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>23 25 00</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>HVAC WATER TREATMENT</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Furnish service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>23 21 13</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>HYDRONIC PIPING</t>
+          <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Special Tool</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
+          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>for every ten plug valves minimum of one</t>
+          <t>monthly - count not stated in this sentence, estimator must compute it</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Operator: One plug valve wrench for every ten plug valves minimum of one.</t>
+          <t>Provide monthly technical service visits to perform field inspections and make water analysis on site.</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2561,7 +2585,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L42" s="4" t="n"/>
@@ -2571,43 +2595,39 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>23 21 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>HYDRONIC PUMPS</t>
+          <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Extra Pump Seals</t>
+          <t>two copies of field service report after each visit</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>for each type and size of pump</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Extra Pump Seals: One set for each type and size of pump.</t>
+          <t>Submit two copies of field service report after each visit.</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2617,7 +2637,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L43" s="4" t="n"/>
@@ -2625,112 +2645,94 @@
       <c r="N43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, </t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="n">
         <v>398</v>
       </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Furnish service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Include 2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, and operation of water treatment systems.</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="n">
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>sufficient chemicals for treatment and testing during warranty period</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="n">
         <v>398</v>
       </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Provide monthly technical service visits to perform field inspections and make water analysis on site.</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Supply sufficient chemicals for treatment and testing during warranty period.</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2745,29 +2747,23 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>two copies of field service report after each visit</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Submit two copies of field service report after each visit.</t>
+          <t>Training: Train Owner's personnel on operation and maintenance of chemical treatment system.</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2802,7 +2798,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, </t>
+          <t>two hours of instruction for two people</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
@@ -2813,13 +2809,17 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H47" s="3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Include 2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, and operation of water treatment systems.</t>
+          <t>Provide minimum of two hours of instruction for two people.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2833,46 +2833,60 @@
       <c r="N47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>sufficient chemicals for treatment and testing during warranty period</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="n">
-        <v>398</v>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>Supply sufficient chemicals for treatment and testing during warranty period.</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="N48" s="3" t="n"/>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Provide service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2887,23 +2901,33 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
+          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>bi-monthly - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
       <c r="H49" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of chemical treatment system.</t>
+          <t>Provide bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and make water analysis on site.</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -2913,7 +2937,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L49" s="4" t="n"/>
@@ -2923,43 +2947,39 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>HVAC WATER TREATMENT</t>
+          <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>two hours of instruction for two people</t>
+          <t>Extra Refrigerant</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="3" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum of two hours of instruction for two people.</t>
+          <t>Extra Refrigerant: One container.</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -2973,160 +2993,150 @@
       <c r="N50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>23 25 00</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>HVAC WATER TREATMENT</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>23 64 23</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>SCROLL WATER CHILLER</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Extra Lubricating Oil</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Extra Lubricating Oil: One container.</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>23 64 23</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>SCROLL WATER CHILLER</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>Provide service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty: Provide minimum Five year warranty to include coverage for materials and labor for compressor.</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="n"/>
+      <c r="M52" s="3" t="n"/>
+      <c r="N52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>23 64 23</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>SCROLL WATER CHILLER</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>23 25 00</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>HVAC WATER TREATMENT</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>Provide bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and make water analysis on site.</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>23 64 23</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>SCROLL WATER CHILLER</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Extra Refrigerant</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="n">
-        <v>414</v>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>Extra Refrigerant: One container.</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="N53" s="3" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3141,29 +3151,33 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Extra Lubricating Oil</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H54" s="3" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Extra Lubricating Oil: One container.</t>
+          <t>Provide minimum of two hours of training.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -3177,143 +3191,145 @@
       <c r="N54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>23 64 23</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>414</v>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty: Provide minimum Five year warranty to include coverage for materials and labor for compressor.</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>23 64 26</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Extra Refrigerant</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Extra Refrigerant: One container.</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="n"/>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="3" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>23 64 23</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>SCROLL WATER CHILLER</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="4" t="n">
-        <v>418</v>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="n"/>
-      <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" s="3" t="n"/>
+      <c r="N56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>SCROLL WATER CHILLER</t>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>Extra Lubricating Oil</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="3" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum of two hours of training.</t>
+          <t>Extra Lubricating Oil: One container.</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -3327,60 +3343,52 @@
       <c r="N57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>23 64 23</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>SCROLL WATER CHILLER</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>separate maintenance contract for the service and maintenance of chiller for 2years from Date of Substantial C</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="n">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>23 64 26</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>418</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty: 2 year parts and labor warranty for entire system.</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" s="3" t="n"/>
+      <c r="N58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -3395,29 +3403,33 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Extra Refrigerant</t>
+          <t>five year warranty to include coverage for materials only for compressor</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H59" s="3" t="n">
         <v>420</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Extra Refrigerant: One container.</t>
+          <t>Provide minimum five year warranty to include coverage for materials only for compressor.</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -3431,52 +3443,50 @@
       <c r="N59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>23 64 26</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Extra Lubricating Oil</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>Extra Lubricating Oil: One container.</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr"/>
-      <c r="L60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="n">
+        <v>424</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -3491,12 +3501,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Manufacturer's Warranty</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3504,16 +3514,20 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H61" s="3" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Manufacturer's Warranty: 2 year parts and labor warranty for entire system.</t>
+          <t>Provide minimum of two hours of training.</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -3527,87 +3541,101 @@
       <c r="N61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>23 64 26</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>five year warranty to include coverage for materials only for compressor</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum five year warranty to include coverage for materials only for compressor.</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr"/>
-      <c r="L62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>424</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
+      <c r="N62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 73 13</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
+          <t>Extra Fan Belts</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>for each unit</t>
+        </is>
+      </c>
       <c r="H63" s="4" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+          <t>Extra Fan Belts: One set for each unit.</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3617,7 +3645,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L63" s="4" t="n"/>
@@ -3625,260 +3653,270 @@
       <c r="N63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>23 64 26</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Extra Filters</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>for each unit</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Extra Filters: One set for each unit.</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or wo</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>426</v>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Provide minimum two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or workmanship.</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="n"/>
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>two hours of training</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>one day of training</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Provide minimum of one day of training.</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>424</v>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum of two hours of training.</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr"/>
-      <c r="L64" s="3" t="n"/>
-      <c r="M64" s="3" t="n"/>
-      <c r="N64" s="3" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>23 64 26</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>from Date of Substantial Completion</t>
         </is>
       </c>
-      <c r="H65" s="4" t="n">
-        <v>424</v>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="H68" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Provide service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Extra Fan Belts</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="n">
-        <v>426</v>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>Extra Fan Belts: One setfor each unit.</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr"/>
-      <c r="L66" s="3" t="n"/>
-      <c r="M66" s="3" t="n"/>
-      <c r="N66" s="3" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Extra Filters</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="n">
-        <v>426</v>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>Extra Filters: One setfor each unit.</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="3" t="n"/>
-      <c r="M67" s="3" t="n"/>
-      <c r="N67" s="3" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or wo</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>426</v>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or workmanship.</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr"/>
-      <c r="L68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="3" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -3893,23 +3931,33 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
+          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>three month interval - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
       <c r="H69" s="4" t="n">
         <v>432</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+          <t>Provide routine maintenance service with a three month interval as maximum time period between calls.</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -3939,20 +3987,20 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>one day of training</t>
+          <t xml:space="preserve">filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -3961,11 +4009,11 @@
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Provide minimum of one day of training.</t>
+          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -3975,7 +4023,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L70" s="4" t="n"/>
@@ -4000,28 +4048,28 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
+          <t xml:space="preserve">fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>YR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>from Date of Substantial Completion</t>
+          <t>minimum</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Provide service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion.</t>
+          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4039,253 +4087,241 @@
       <c r="N71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr"/>
-      <c r="H72" s="4" t="n">
-        <v>432</v>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>Provide routine maintenance service with a three month interval as maximum time period between calls.</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>23 81 01</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>five year manufacturers warranty for all motors</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Provide five year manufacturers warranty for all motors.</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>23 81 01</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>one year parts and labor warranty for enitre unit, from substitute and completion</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Provide one year parts and labor warranty for enitre unit, from substitute and completion.</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="n"/>
+      <c r="M73" s="3" t="n"/>
+      <c r="N73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>23 81 01</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>one (1) set of filters, with a final change immediately prior to occupancy</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Provide one (1) set of filters, with a final change immediately prior to occupancy.</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="n"/>
+      <c r="M74" s="3" t="n"/>
+      <c r="N74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>26 27 26</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>WIRING DEVICES</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>two of each style, size, and finish wall plate</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>of each style</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>479</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Furnish two of each style, size, and finish wall plate.</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="n">
-        <v>433</v>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>433</v>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>23 81 01</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>five year manufacturers warranty for all motors</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>Provide five year manufacturers warranty for all motors.</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>23 81 01</t>
+          <t>26 28 13</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
+          <t>FUSES</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Special Tool</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>one year parts and labor warranty for enitre unit, from substitute and completion</t>
+          <t>two fuse pullers</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="3" t="n">
-        <v>435</v>
+        <v>483</v>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Provide one year parts and labor warranty for enitre unit, from substitute and completion.</t>
+          <t>Furnish two fuse pullers.</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -4299,215 +4335,63 @@
       <c r="N76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>23 81 01</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>one (1)set of filters, with a final change immediately prior to occupancy</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>Provide one (1)set of filters, with a final change immediately prior to occupancy.</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr"/>
-      <c r="L77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
-      <c r="N77" s="3" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>26 27 26</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>WIRING DEVICES</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>two of each style, size, and finish wall plate</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>26 28 13</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>FUSES</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>three of each size and type fuse installed</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>of each style</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>479</v>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>Furnish two of each style, size, and finish wall plate.</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>of each size and type fuse installed</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>483</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Furnish three of each size and type fuse installed.</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L78" s="4" t="n"/>
-      <c r="M78" s="4" t="n"/>
-      <c r="N78" s="4" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>26 28 13</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>FUSES</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Special Tool</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>two fuse pullers</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="n">
-        <v>483</v>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>Furnish two fuse pullers.</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr"/>
-      <c r="L79" s="3" t="n"/>
-      <c r="M79" s="3" t="n"/>
-      <c r="N79" s="3" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>26 28 13</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>FUSES</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>three of each size and type fuse installed</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>of each size and type fuse installed</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="n">
-        <v>483</v>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>Furnish three of each size and type fuse installed.</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="n"/>
-      <c r="M80" s="4" t="n"/>
-      <c r="N80" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
+      <c r="N77" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N80"/>
+  <autoFilter ref="A2:N77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4544,7 +4428,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -4560,21 +4444,21 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -4624,7 +4508,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4638,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4701,19 +4585,19 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>01 40 00</t>
+          <t>01 70 00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>When specified in individual specification sections, require material or product suppliers or manufacturers to</t>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -4740,7 +4624,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -4752,7 +4636,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+          <t>qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's pe</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -4779,7 +4663,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4791,7 +4675,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's pe</t>
+          <t>8 hours minimum of demonstration and training</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4801,24 +4685,26 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n"/>
+          <t>8 h</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -4826,57 +4712,55 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>8 hours minimum of demonstration and training</t>
+          <t>Maintenance Period</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>8 h</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>8</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>01 70 00</t>
+          <t>01 79 00</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Maintenance Period</t>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -4898,7 +4782,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -4910,7 +4794,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+          <t>8 hours of training</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -4920,87 +4804,87 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n"/>
+          <t>8 h</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>23 09 13</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>258</v>
+        <v>352</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>8 hours of training</t>
+          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>8 h</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>8</v>
-      </c>
+          <t>two year period</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Training schedule will be subject to availability of Owner's personnel to be trained; re-schedule training ses</t>
+          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>one year period</t>
         </is>
       </c>
       <c r="G9" s="3" t="n"/>
@@ -5017,29 +4901,29 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>259</v>
+        <v>354</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Be prepared to answer questions raised by training attendees; if unable to answer during training session, pro</t>
+          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3 day(s)</t>
+          <t>4 inspections; per year</t>
         </is>
       </c>
       <c r="G10" s="3" t="n"/>
@@ -5050,25 +4934,25 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>3 day(s) stated - hours per day not stated in spec</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>23 09 13</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
+          <t xml:space="preserve">Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5078,24 +4962,26 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>two year period</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+          <t>4 h; 4 inspections</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>4 x 4 h stated</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -5103,21 +4989,21 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
+          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>one year period</t>
+          <t>2 day(s)</t>
         </is>
       </c>
       <c r="G12" s="3" t="n"/>
@@ -5128,13 +5014,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -5142,50 +5028,52 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
+          <t>minimum of 8 hours dedicated instructor time</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>4 inspections; per year</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n"/>
+          <t>8 h</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service </t>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -5195,48 +5083,46 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>4 h; 4 inspections</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>16</v>
-      </c>
+          <t>one year period</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>4 x 4 h stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
+          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2 day(s)</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="G15" s="3" t="n"/>
@@ -5247,54 +5133,52 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>2 day(s) stated - hours per day not stated in spec</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>minimum of 8 hours dedicated instructor time</t>
+          <t>two copies of field service report after each visit</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>8 h</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>8</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -5306,28 +5190,30 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+          <t xml:space="preserve">2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>one year period</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n"/>
+          <t>2 h</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
@@ -5341,21 +5227,21 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
@@ -5380,32 +5266,34 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>two copies of field service report after each visit</t>
+          <t>two hours of instruction for two people</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n"/>
+          <t>2 h; 2 person(s)</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated (instructor hours; 2 trainees = 4 trainee-hours)</t>
         </is>
       </c>
     </row>
@@ -5419,40 +5307,38 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, </t>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2 h</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>one year period</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -5460,21 +5346,21 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>bi-monthly</t>
         </is>
       </c>
       <c r="G21" s="3" t="n"/>
@@ -5491,19 +5377,19 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>two hours of instruction for two people</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -5513,77 +5399,77 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2 h; 2 person(s)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>hours stated (instructor hours; 2 trainees = 4 trainee-hours)</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>one year period</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n"/>
+          <t>2 h</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
+          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -5593,7 +5479,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>bi-monthly</t>
+          <t>2 year period</t>
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
@@ -5610,15 +5496,15 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -5649,15 +5535,15 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -5690,19 +5576,19 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>separate maintenance contract for the service and maintenance of chiller for 2years from Date of Substantial C</t>
+          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -5729,15 +5615,15 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 73 13</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -5768,19 +5654,19 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 73 13</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>one day of training</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -5790,38 +5676,36 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2 h</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>1 day(s)</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>1 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 73 13</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
+          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5848,7 +5732,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -5860,17 +5744,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>three month interval</t>
         </is>
       </c>
       <c r="G31" s="3" t="n"/>
@@ -5887,7 +5771,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -5895,21 +5779,21 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>one day of training</t>
+          <t xml:space="preserve">filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1 day(s)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G32" s="3" t="n"/>
@@ -5920,13 +5804,13 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>1 day(s) stated - hours per day not stated in spec</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -5934,11 +5818,11 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
+          <t xml:space="preserve">fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -5948,7 +5832,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2 year period</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" s="3" t="n"/>
@@ -5958,123 +5842,6 @@
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>432</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Post-completion service</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>three month interval</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>433</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Post-completion service</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>433</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Post-completion service</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
@@ -6091,7 +5858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6130,15 +5897,15 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>R2 quote not found on page 143</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
@@ -6154,7 +5921,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -6174,7 +5941,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -6194,7 +5961,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -6214,7 +5981,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -6234,7 +6001,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -6254,7 +6021,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -6274,7 +6041,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -6294,7 +6061,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -6305,20 +6072,20 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2 Quality</t>
+          <t>1 Precision</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>R6 duplicate of row 45</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
     </row>
@@ -6334,11 +6101,11 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>R6 quote repeated without a distinct item (padding)</t>
+          <t>R6 duplicate of row 41</t>
         </is>
       </c>
     </row>
@@ -6350,15 +6117,15 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI</t>
+          <t>R6 quote repeated without a distinct item (padding)</t>
         </is>
       </c>
     </row>
@@ -6374,11 +6141,11 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI</t>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI</t>
         </is>
       </c>
     </row>
@@ -6393,14 +6160,12 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>47</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>R11 page 18: closeout keywords but no row - review manually</t>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6187,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>R11 page 130: closeout keywords but no row - review manually</t>
+          <t>R11 page 18: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6209,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>R11 page 166: closeout keywords but no row - review manually</t>
+          <t>R11 page 130: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6231,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>R11 page 235: closeout keywords but no row - review manually</t>
+          <t>R11 page 166: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6253,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>R11 page 348: closeout keywords but no row - review manually</t>
+          <t>R11 page 235: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6275,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>R11 page 381: closeout keywords but no row - review manually</t>
+          <t>R11 page 259: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6297,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>R11 page 397: closeout keywords but no row - review manually</t>
+          <t>R11 page 348: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6319,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>R11 page 469: closeout keywords but no row - review manually</t>
+          <t>R11 page 381: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6341,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>R11 page 488: closeout keywords but no row - review manually</t>
+          <t>R11 page 397: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6353,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -6598,7 +6363,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>48 intentionally blank pages skipped</t>
+          <t>R11 page 469: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6375,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -6620,14 +6385,14 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>80 candidate rows from 509 pages: Maintenance Service 17, Extended Warranty 14, O&amp;M Deliverable 12, Quantity Not Specified 12, Training 9, Spare Part 9, Attic Stock 5, Special Tool 2</t>
+          <t>R11 page 488: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6 Drawings</t>
+          <t>2 Quality</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6642,47 +6407,51 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0 per-unit rows totalled from drawings/counts, 10 still need a count</t>
+          <t>48 intentionally blank pages skipped</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>2 Quality</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>8</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>76 candidate rows from 509 pages: Maintenance Service 16, Extended Warranty 14, O&amp;M Deliverable 11, Quantity Not Specified 10, Training 9, Spare Part 9, Attic Stock 5, Special Tool 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>6 Drawings</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>9</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>0 per-unit rows totalled from drawings/counts, 10 still need a count</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6467,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -6718,7 +6487,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -6738,7 +6507,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -6758,7 +6527,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -6778,11 +6547,11 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 3 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6567,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -6818,7 +6587,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -6838,11 +6607,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6631,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6647,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -6898,7 +6667,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -6918,7 +6687,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -6938,7 +6707,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -6958,7 +6727,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -6978,7 +6747,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -6998,7 +6767,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -7018,7 +6787,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -7038,7 +6807,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -7078,11 +6847,11 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
@@ -7098,11 +6867,11 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -7118,7 +6887,7 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -7138,7 +6907,7 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -7158,7 +6927,7 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -7174,27 +6943,29 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>74</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>32 labor items; 8 computed from spec (48 h stated), 24 need estimator input</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>8 Div 23/26</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -7204,7 +6975,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>35 labor items; 8 computed from spec (48 h stated), 27 need estimator input</t>
+          <t>R16 26 28 18 ENCLOSED SWITCHES: calls for maintenance materials but lists none - RFI</t>
         </is>
       </c>
     </row>
@@ -7216,7 +6987,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -7226,7 +6997,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>R16 26 28 18 ENCLOSED SWITCHES: calls for maintenance materials but lists none - RFI</t>
+          <t>R16 Division 23 HVAC: 21 sections, 12 with requirements, 0 flagged CHECK</t>
         </is>
       </c>
     </row>
@@ -7248,14 +7019,14 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>R16 Division 23 HVAC: 21 sections, 12 with requirements, 0 flagged CHECK</t>
+          <t>R16 Division 26 Electrical: 12 sections, 2 with requirements, 1 flagged CHECK</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8 Div 23/26</t>
+          <t>4 Delivery</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7270,29 +7041,27 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>R16 Division 26 Electrical: 12 sections, 2 with requirements, 1 flagged CHECK</t>
+          <t>R12 file re-opened and matches verified data (75 rows)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4 Delivery</t>
+          <t>7 Language</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>R12 file re-opened and matches verified data (78 rows)</t>
+          <t>R15 quote has no common English words - check source</t>
         </is>
       </c>
     </row>
@@ -7304,22 +7073,24 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>34</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>R15 quote has no common English words - check source</t>
+          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>7 Language</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -7333,28 +7104,6 @@
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Extraction and checks took 17 seconds</t>
         </is>

--- a/spectakeoff/RCCD_Closeout_Schedule.xlsx
+++ b/spectakeoff/RCCD_Closeout_Schedule.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source: RCCD.pdf (509 pages) - 75 requirements. Every quote verified word-for-word against the cited page.</t>
+          <t>Source: RCCD.pdf (509 pages) - 78 requirements. Every quote verified word-for-word against the cited page.</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Performance and Payment Bonds shall be maintained in full force (warranty bond) for a period of two (2) years </t>
+          <t>Performance and Payment Bonds shall be maintained in full force (warranty bond) for a period of two (2) years</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -863,96 +863,88 @@
       <c r="N8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="n">
-        <v>244</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>copy of site drawing signed by the Land Surveyor, that the elevations and locations of the work are in complia</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Submit a copy of site drawing signed by the Land Surveyor, that the elevations and locations of the work are in compliance with Contract Documents.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's pe</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="n">
-        <v>244</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Provide a qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's personnel.</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>surveys and survey logs for the project record</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Submit surveys and survey logs for the project record.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -967,33 +959,23 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>8 hours minimum of demonstration and training</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>written report that equipment or system has been properly installed and is functioning correctly</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="n">
         <v>244</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Provide 8 hours minimum of demonstration and training.</t>
+          <t>Submit a written report that equipment or system has been properly installed and is functioning correctly.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1007,52 +989,50 @@
       <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>bound hardcopies - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1067,29 +1047,33 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>archival-grade (gold foil) DVDs - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
+          <t>8 hours minimum of demonstration and training</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
+          <t>Provide 8 hours minimum of demonstration and training.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1103,70 +1087,62 @@
       <c r="N13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Period</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>from the Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>bound hardcopies - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Period: As indicated in specification sections or, if not indicated, not less than one year from the Date of Substantial Completion or the length of the specified warranty, whichever is longer.</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>01 78 00</t>
+          <t>01 70 00</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CLOSEOUT SUBMITTALS</t>
+          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1176,7 +1152,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>two sets of revised final documents in final form within 10 days after final inspection</t>
+          <t>archival-grade (gold foil) DVDs - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -1184,16 +1160,16 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Submit two sets of revised final documents in final form within 10 days after final inspection.</t>
+          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1209,39 +1185,33 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>01 78 00</t>
+          <t>01 70 00</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>CLOSEOUT SUBMITTALS</t>
+          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
+          <t>written certification that Contract Documents have been reviewed, work has been inspected, and that work is co</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
+          <t>Submit written certification that Contract Documents have been reviewed, work has been inspected, and that work is complete in accordance with Contract Documents and ready for Architect's review.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,52 +1225,60 @@
       <c r="N16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>01 78 00</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>CLOSEOUT SUBMITTALS</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>01 70 00</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Period</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>from the Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Period: As indicated in specification sections or, if not indicated, not less than one year from the Date of Substantial Completion or the length of the specified warranty, whichever is longer.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1320,7 +1298,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, withi</t>
+          <t>two sets of revised final documents in final form within 10 days after final inspection</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -1328,16 +1306,16 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Obtain warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, within 10 days after completion of the applicable item of work.</t>
+          <t>Submit two sets of revised final documents in final form within 10 days after final inspection.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1351,347 +1329,347 @@
       <c r="N18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>01 78 00</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEOUT SUBMITTALS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>01 78 00</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEOUT SUBMITTALS</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>01 78 00</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEOUT SUBMITTALS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, withi</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Obtain warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, within 10 days after completion of the applicable item of work.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Training Manuals</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>for each attendee</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>257</v>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Training Manuals: Provide training manual for each attendee; allow for minimum of two attendees per training session.</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>one extra copy of each training manual to be included with operation and maintenance data</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>of each training manual to be included with operation and maintenance data</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>257</v>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Provide one extra copy of each training manual to be included with operation and maintenance data.</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="n">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
         <v>258</v>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>8 hours of training</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum 8 hours of training.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>03 30 00</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>CAST IN PLACE CONCRETE</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA)</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA): Provide warranty to cover the cost of flooring failures due to moisture migration from slabs for ten years.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>03 30 00</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>CAST IN PLACE CONCRETE</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Moisture Emission Reducing Curing and Sealing Compound</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Moisture Emission Reducing Curing and Sealing Compound: Provide warranty to cost of flooring delamination failures for 10 years.</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>09 51 00</t>
+          <t>01 79 00</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>ACOUSTICAL CEILINGS</t>
+          <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project</t>
+          <t>8 hours of training</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="n">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Provide 100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project.</t>
+          <t>Provide minimum 8 hours of training.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1707,39 +1685,39 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>09 51 00</t>
+          <t>03 30 00</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ACOUSTICAL CEILINGS</t>
+          <t>CAST IN PLACE CONCRETE</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>1 box of Type A2 acoustical unit, for Owner's use in maintenance of project</t>
+          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA)</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="n">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Provide 1 box of Type A2 acoustical unit, for Owner's use in maintenance of project.</t>
+          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA): Provide warranty to cover the cost of flooring failures due to moisture migration from slabs for ten years.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1753,97 +1731,89 @@
       <c r="N26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>09 90 00</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>PAINTS AND COATINGS</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>1 gallon of each color; store where directed</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>GAL</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>of each color</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>296</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Supply 1 gallon of each color; store where directed.</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>03 30 00</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>CAST IN PLACE CONCRETE</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Moisture Emission Reducing Curing and Sealing Compound</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Moisture Emission Reducing Curing and Sealing Compound: Provide warranty to cost of flooring delamination failures for 10 years.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>23 05 13</t>
+          <t>09 51 00</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>MOTOR REQUIREMENTS FOR HVAC AND PLUMBING EQUIPMENT</t>
+          <t>ACOUSTICAL CEILINGS</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Attic Stock</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>five year manufacturer warranty for motors larger than 20 horsepower</t>
+          <t>100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Provide five year manufacturer warranty for motors larger than 20 horsepower.</t>
+          <t>Provide 100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1857,243 +1827,243 @@
       <c r="N28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>09 51 00</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>ACOUSTICAL CEILINGS</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1 box of Type A2 acoustical unit, for Owner's use in maintenance of project</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Provide 1 box of Type A2 acoustical unit, for Owner's use in maintenance of project.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>09 90 00</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>PAINTS AND COATINGS</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>1 gallon of each color; store where directed</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>GAL</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>of each color</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Supply 1 gallon of each color; store where directed.</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>23 05 13</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>MOTOR REQUIREMENTS FOR HVAC AND PLUMBING EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>five year manufacturer warranty for motors larger than 20 horsepower</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Provide five year manufacturer warranty for motors larger than 20 horsepower.</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>23 05 16</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>EXPANSION FITTINGS AND LOOPS FOR HVAC PIPING</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Spare Part</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>two sets of packing for each packed expansion joint</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>SET</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>for each packed expansion joint</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>309</v>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Supply two sets of packing for each packed expansion joint.</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>23 05 93</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>TESTING, ADJUSTING, AND BALANCING FOR HVAC</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>final copies for Architect and for inclusion in operating and maintenance manuals</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="n">
-        <v>326</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>Provide final copies for Architect and for inclusion in operating and maintenance manuals.</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>23 09 13</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>INSTRUMENTATION AND CONTROL DEVICES FOR HVAC</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>352</v>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Provide service and maintenance of control system for two years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>23 09 23</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>defective Work within a five year period after Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="n">
-        <v>354</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>Correct defective Work within a five year period after Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 05 93</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+          <t>TESTING, ADJUSTING, AND BALANCING FOR HVAC</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>five year manufacturer's warranty for field programmable micro-processor based units</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
+          <t>final copies for Architect and for inclusion in operating and maintenance manuals</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="n">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Provide five year manufacturer's warranty for field programmable micro-processor based units.</t>
+          <t>Provide final copies for Architect and for inclusion in operating and maintenance manuals.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2109,12 +2079,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 09 13</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+          <t>INSTRUMENTATION AND CONTROL DEVICES FOR HVAC</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2124,11 +2094,11 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
+          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -2141,11 +2111,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Provide service and maintenance of energy management and control systems for one years from Date of Substantial Completion.</t>
+          <t>Provide service and maintenance of control system for two years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2163,60 +2133,52 @@
       <c r="N34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>23 09 23</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>per year</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>defective Work within a five year period after Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="n">
         <v>354</v>
       </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Provide four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required, and submit written reports.</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Correct defective Work within a five year period after Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2231,33 +2193,29 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service </t>
+          <t>five year manufacturer's warranty for field programmable micro-processor based units</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="3" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service calls to inspect, calibrate, and adjust controls, and submit written reports.</t>
+          <t>Provide five year manufacturer's warranty for field programmable micro-processor based units.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2283,29 +2241,33 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
+          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>DAY</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr"/>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
       <c r="H37" s="4" t="n">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Provide service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day period.</t>
+          <t>Provide service and maintenance of energy management and control systems for one years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2315,7 +2277,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L37" s="4" t="n"/>
@@ -2323,153 +2285,149 @@
       <c r="N37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>23 09 23</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>minimum of 8 hours dedicated instructor time</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Provide four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required, and submit written reports.</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>23 09 23</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>minimum</t>
         </is>
       </c>
-      <c r="H38" s="3" t="n">
-        <v>373</v>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>Include a minimum of 8 hours dedicated instructor time.</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="H39" s="3" t="n">
+        <v>355</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service calls to inspect, calibrate, and adjust controls, and submit written reports.</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>23 21 13</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>HYDRONIC PIPING</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Special Tool</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>for every ten plug valves minimum of one</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>385</v>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Operator: One plug valve wrench for every ten plug valves minimum of one.</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="n"/>
-      <c r="M39" s="4" t="n"/>
-      <c r="N39" s="4" t="n"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>23 21 23</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>HYDRONIC PUMPS</t>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Extra Pump Seals</t>
+          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>for each type and size of pump</t>
-        </is>
-      </c>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="n">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Extra Pump Seals: One set for each type and size of pump.</t>
+          <t>Provide service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day period.</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2479,7 +2437,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
       <c r="L40" s="4" t="n"/>
@@ -2487,95 +2445,97 @@
       <c r="N40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>23 25 00</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>HVAC WATER TREATMENT</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>398</v>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Furnish service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>23 09 23</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>minimum of 8 hours dedicated instructor time</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Include a minimum of 8 hours dedicated instructor time.</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 21 13</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>HVAC WATER TREATMENT</t>
+          <t>HYDRONIC PIPING</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Special Tool</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="inlineStr"/>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>monthly - count not stated in this sentence, estimator must compute it</t>
+          <t>for every ten plug valves minimum of one</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Provide monthly technical service visits to perform field inspections and make water analysis on site.</t>
+          <t>Operator: One plug valve wrench for every ten plug valves minimum of one.</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2585,7 +2545,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L42" s="4" t="n"/>
@@ -2595,39 +2555,43 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 21 23</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>HVAC WATER TREATMENT</t>
+          <t>HYDRONIC PUMPS</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>two copies of field service report after each visit</t>
+          <t>Extra Pump Seals</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr"/>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>for each type and size of pump</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="n">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Submit two copies of field service report after each visit.</t>
+          <t>Extra Pump Seals: One set for each type and size of pump.</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2637,7 +2601,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L43" s="4" t="n"/>
@@ -2645,94 +2609,110 @@
       <c r="N43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, </t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="n">
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>Include 2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, and operation of water treatment systems.</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Furnish service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>sufficient chemicals for treatment and testing during warranty period</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="n">
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>monthly - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Supply sufficient chemicals for treatment and testing during warranty period.</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Provide monthly technical service visits to perform field inspections and make water analysis on site.</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2747,23 +2727,29 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="inlineStr"/>
+          <t>two copies of field service report after each visit</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of chemical treatment system.</t>
+          <t>Submit two copies of field service report after each visit.</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2798,7 +2784,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>two hours of instruction for two people</t>
+          <t>2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing,</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
@@ -2809,17 +2795,13 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+      <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="3" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum of two hours of instruction for two people.</t>
+          <t>Include 2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, and operation of water treatment systems.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2833,60 +2815,46 @@
       <c r="N47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>Provide service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>sufficient chemicals for treatment and testing during warranty period</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="n">
+        <v>398</v>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Supply sufficient chemicals for treatment and testing during warranty period.</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2901,33 +2869,23 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>bi-monthly - count not stated in this sentence, estimator must compute it</t>
-        </is>
-      </c>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Provide bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and make water analysis on site.</t>
+          <t>Training: Train Owner's personnel on operation and maintenance of chemical treatment system.</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -2937,7 +2895,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L49" s="4" t="n"/>
@@ -2947,39 +2905,43 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>SCROLL WATER CHILLER</t>
+          <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Extra Refrigerant</t>
+          <t>two hours of instruction for two people</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H50" s="3" t="n">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Extra Refrigerant: One container.</t>
+          <t>Provide minimum of two hours of instruction for two people.</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -2993,150 +2955,164 @@
       <c r="N50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>23 25 00</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>HVAC WATER TREATMENT</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Provide service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>23 25 00</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>HVAC WATER TREATMENT</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>bi-monthly - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Provide bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and make water analysis on site.</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>23 64 23</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Spare Part</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Extra Lubricating Oil</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Extra Refrigerant</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="n">
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="n">
         <v>414</v>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Extra Lubricating Oil: One container.</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Extra Refrigerant: One container.</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr"/>
-      <c r="L51" s="3" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>23 64 23</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>SCROLL WATER CHILLER</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>414</v>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty: Provide minimum Five year warranty to include coverage for materials and labor for compressor.</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr"/>
-      <c r="L52" s="3" t="n"/>
-      <c r="M52" s="3" t="n"/>
-      <c r="N52" s="3" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>23 64 23</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>SCROLL WATER CHILLER</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="4" t="n">
-        <v>418</v>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3151,33 +3127,29 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>Extra Lubricating Oil</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum of two hours of training.</t>
+          <t>Extra Lubricating Oil: One container.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -3191,145 +3163,143 @@
       <c r="N54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>23 64 23</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="n">
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty: Provide minimum Five year warranty to include coverage for materials and labor for compressor.</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>23 64 23</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>SCROLL WATER CHILLER</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="n">
         <v>418</v>
       </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>23 64 26</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Extra Refrigerant</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>Extra Refrigerant: One container.</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr"/>
-      <c r="L56" s="3" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="3" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
+          <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Extra Lubricating Oil</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H57" s="3" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Extra Lubricating Oil: One container.</t>
+          <t>Provide minimum of two hours of training.</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -3343,52 +3313,60 @@
       <c r="N57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>23 64 26</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>23 64 23</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>SCROLL WATER CHILLER</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty: 2 year parts and labor warranty for entire system.</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr"/>
-      <c r="L58" s="3" t="n"/>
-      <c r="M58" s="3" t="n"/>
-      <c r="N58" s="3" t="n"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -3403,33 +3381,29 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>five year warranty to include coverage for materials only for compressor</t>
+          <t>Extra Refrigerant</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="3" t="n">
         <v>420</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum five year warranty to include coverage for materials only for compressor.</t>
+          <t>Extra Refrigerant: One container.</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -3443,50 +3417,52 @@
       <c r="N59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>23 64 26</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="n">
-        <v>424</v>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Extra Lubricating Oil</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Extra Lubricating Oil: One container.</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -3501,12 +3477,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>Manufacturer's Warranty</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3514,20 +3490,16 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="3" t="n">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum of two hours of training.</t>
+          <t>Manufacturer's Warranty: 2 year parts and labor warranty for entire system.</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -3541,101 +3513,87 @@
       <c r="N61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>23 64 26</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>five year warranty to include coverage for materials only for compressor</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>424</v>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Provide minimum five year warranty to include coverage for materials only for compressor.</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>23 73 13</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Extra Fan Belts</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>for each unit</t>
-        </is>
-      </c>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Extra Fan Belts: One set for each unit.</t>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3645,7 +3603,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L63" s="4" t="n"/>
@@ -3653,112 +3611,112 @@
       <c r="N63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Extra Filters</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>for each unit</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>426</v>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>Extra Filters: One set for each unit.</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>23 64 26</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>two hours of training</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Provide minimum of two hours of training.</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="n"/>
+      <c r="M64" s="3" t="n"/>
+      <c r="N64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>23 64 26</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>424</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or wo</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>426</v>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or workmanship.</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="n"/>
-      <c r="M65" s="3" t="n"/>
-      <c r="N65" s="3" t="n"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -3773,23 +3731,33 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
+          <t>Extra Fan Belts</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>for each unit</t>
+        </is>
+      </c>
       <c r="H66" s="4" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+          <t>Extra Fan Belts: One set for each unit.</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -3799,7 +3767,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L66" s="4" t="n"/>
@@ -3819,12 +3787,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>one day of training</t>
+          <t>Extra Filters</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -3832,20 +3800,20 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>minimum</t>
+          <t>for each unit</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Provide minimum of one day of training.</t>
+          <t>Extra Filters: One set for each unit.</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -3855,7 +3823,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L67" s="4" t="n"/>
@@ -3863,60 +3831,56 @@
       <c r="N67" s="4" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>23 73 13</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="n">
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or wo</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>432</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>Provide service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>426</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Provide minimum two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or workmanship.</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="n"/>
+      <c r="M68" s="3" t="n"/>
+      <c r="N68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -3931,33 +3895,23 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>three month interval - count not stated in this sentence, estimator must compute it</t>
-        </is>
-      </c>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="n">
         <v>432</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Provide routine maintenance service with a three month interval as maximum time period between calls.</t>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -3987,20 +3941,20 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
+          <t>one day of training</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -4009,11 +3963,11 @@
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
+          <t>Provide minimum of one day of training.</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -4023,7 +3977,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
       <c r="L70" s="4" t="n"/>
@@ -4048,28 +4002,28 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
+          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>minimum</t>
+          <t>from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
+          <t>Provide service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4087,241 +4041,257 @@
       <c r="N71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>three month interval - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Provide routine maintenance service with a three month interval as maximum time period between calls.</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>433</v>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>433</v>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>23 81 01</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>TERMINAL HEAT TRANSFER UNITS</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Extended Warranty</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>five year manufacturers warranty for all motors</t>
         </is>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E75" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="n">
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="n">
         <v>435</v>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>Provide five year manufacturers warranty for all motors.</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr"/>
-      <c r="L72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>23 81 01</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>one year parts and labor warranty for enitre unit, from substitute and completion</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>Provide one year parts and labor warranty for enitre unit, from substitute and completion.</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr"/>
-      <c r="L73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>23 81 01</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>one (1) set of filters, with a final change immediately prior to occupancy</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>Provide one (1) set of filters, with a final change immediately prior to occupancy.</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr"/>
-      <c r="L74" s="3" t="n"/>
-      <c r="M74" s="3" t="n"/>
-      <c r="N74" s="3" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>26 27 26</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>WIRING DEVICES</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>two of each style, size, and finish wall plate</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>of each style</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>479</v>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>Furnish two of each style, size, and finish wall plate.</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="4" t="n"/>
-      <c r="N75" s="4" t="n"/>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="n"/>
+      <c r="M75" s="3" t="n"/>
+      <c r="N75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26 28 13</t>
+          <t>23 81 01</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>FUSES</t>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Special Tool</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>two fuse pullers</t>
+          <t>one year parts and labor warranty for enitre unit, from substitute and completion</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="3" t="n">
-        <v>483</v>
+        <v>435</v>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Furnish two fuse pullers.</t>
+          <t>Provide one year parts and labor warranty for enitre unit, from substitute and completion.</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -4335,63 +4305,215 @@
       <c r="N76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>23 81 01</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>one (1) set of filters, with a final change immediately prior to occupancy</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Provide one (1) set of filters, with a final change immediately prior to occupancy.</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="n"/>
+      <c r="M77" s="3" t="n"/>
+      <c r="N77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>26 27 26</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>WIRING DEVICES</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>two of each style, size, and finish wall plate</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>of each style</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>479</v>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Furnish two of each style, size, and finish wall plate.</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>26 28 13</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>FUSES</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Special Tool</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>two fuse pullers</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="n">
+        <v>483</v>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Furnish two fuse pullers.</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="n"/>
+      <c r="M79" s="3" t="n"/>
+      <c r="N79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>26 28 13</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>FUSES</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Spare Part</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>three of each size and type fuse installed</t>
         </is>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E80" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>of each size and type fuse installed</t>
         </is>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H80" s="4" t="n">
         <v>483</v>
       </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>Furnish three of each size and type fuse installed.</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="4" t="n"/>
-      <c r="N77" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N77"/>
+  <autoFilter ref="A2:N80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4444,21 +4566,21 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -4508,7 +4630,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -4522,7 +4644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4585,7 +4707,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -4624,7 +4746,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -4636,7 +4758,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>qualified person who is knowledgeable about the Project to perform demonstration and instruction of Owner's pe</t>
+          <t>8 hours minimum of demonstration and training</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -4646,24 +4768,26 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n"/>
+          <t>8 h</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4671,57 +4795,55 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>8 hours minimum of demonstration and training</t>
+          <t>Maintenance Period</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>8 h</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>8</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>01 70 00</t>
+          <t>01 79 00</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Maintenance Period</t>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -4743,7 +4865,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -4755,7 +4877,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+          <t>8 hours of training</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -4765,77 +4887,77 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n"/>
+          <t>8 h</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>01 79 00</t>
+          <t>23 09 13</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>258</v>
+        <v>352</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>8 hours of training</t>
+          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>8 h</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>8</v>
-      </c>
+          <t>two year period</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>23 09 13</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
+          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4845,7 +4967,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>two year period</t>
+          <t>one year period</t>
         </is>
       </c>
       <c r="G8" s="3" t="n"/>
@@ -4862,7 +4984,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -4874,7 +4996,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
+          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4884,7 +5006,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>one year period</t>
+          <t>4 inspections; per year</t>
         </is>
       </c>
       <c r="G9" s="3" t="n"/>
@@ -4901,7 +5023,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -4909,11 +5031,11 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
+          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -4923,24 +5045,26 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>4 inspections; per year</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
+          <t>4 h; 4 inspections</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>4 x 4 h stated</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -4948,40 +5072,38 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service </t>
+          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>4 h; 4 inspections</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>16</v>
-      </c>
+          <t>2 day(s)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>4 x 4 h stated</t>
+          <t>2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -4989,11 +5111,11 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
+          <t>minimum of 8 hours dedicated instructor time</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -5003,65 +5125,65 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2 day(s)</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n"/>
+          <t>8 h</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2 day(s) stated - hours per day not stated in spec</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>minimum of 8 hours dedicated instructor time</t>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>8 h</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8</v>
-      </c>
+          <t>one year period</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -5073,7 +5195,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -5083,7 +5205,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>one year period</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="G14" s="3" t="n"/>
@@ -5100,7 +5222,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -5112,7 +5234,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
+          <t>two copies of field service report after each visit</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -5122,7 +5244,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" s="3" t="n"/>
@@ -5139,7 +5261,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -5151,34 +5273,36 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>two copies of field service report after each visit</t>
+          <t>2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing,</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n"/>
+          <t>2 h</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -5186,11 +5310,11 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, </t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -5200,26 +5324,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2 h</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -5231,7 +5353,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>two hours of instruction for two people</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -5241,24 +5363,26 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
+          <t>2 h; 2 person(s)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated (instructor hours; 2 trainees = 4 trainee-hours)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -5266,40 +5390,38 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>two hours of instruction for two people</t>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2 h; 2 person(s)</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>one year period</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>hours stated (instructor hours; 2 trainees = 4 trainee-hours)</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -5311,7 +5433,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -5321,7 +5443,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>one year period</t>
+          <t>bi-monthly</t>
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
@@ -5338,29 +5460,29 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>bi-monthly</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G21" s="3" t="n"/>
@@ -5377,7 +5499,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -5389,7 +5511,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -5399,24 +5521,26 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n"/>
+          <t>2 h</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -5428,58 +5552,56 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2 h</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>2 year period</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2 year period</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
@@ -5496,7 +5618,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -5508,7 +5630,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -5518,24 +5640,26 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
+          <t>2 h</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Needs input</t>
+          <t>Computed from spec</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>hours stated</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -5547,58 +5671,56 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2 h</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>2 year period</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Computed from spec</t>
+          <t>Needs input</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>hours stated</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 73 13</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial </t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Post-completion service</t>
+          <t>Owner training</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2 year period</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" s="3" t="n"/>
@@ -5615,7 +5737,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -5627,7 +5749,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>one day of training</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -5637,7 +5759,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 day(s)</t>
         </is>
       </c>
       <c r="G28" s="3" t="n"/>
@@ -5648,13 +5770,13 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
+          <t>1 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -5666,17 +5788,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>one day of training</t>
+          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Owner training</t>
+          <t>Post-completion service</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>1 day(s)</t>
+          <t>2 year period</t>
         </is>
       </c>
       <c r="G29" s="3" t="n"/>
@@ -5687,13 +5809,13 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>1 day(s) stated - hours per day not stated in spec</t>
+          <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -5705,7 +5827,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
+          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5715,7 +5837,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2 year period</t>
+          <t>three month interval</t>
         </is>
       </c>
       <c r="G30" s="3" t="n"/>
@@ -5732,7 +5854,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -5740,11 +5862,11 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
+          <t>filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -5754,7 +5876,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>three month interval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G31" s="3" t="n"/>
@@ -5771,7 +5893,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -5783,7 +5905,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
+          <t>fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5803,45 +5925,6 @@
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>433</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including </t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Post-completion service</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Needs input</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>spec states the obligation but not the hours - estimator must price it</t>
         </is>
@@ -5858,7 +5941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5901,7 +5984,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -5921,7 +6004,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -5941,7 +6024,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -5961,7 +6044,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -5981,7 +6064,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -6001,7 +6084,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -6021,7 +6104,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -6041,7 +6124,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -6061,7 +6144,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -6081,7 +6164,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -6101,11 +6184,11 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>R6 duplicate of row 41</t>
+          <t>R6 duplicate of row 44</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6204,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -6141,7 +6224,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -6161,7 +6244,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -6429,7 +6512,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>76 candidate rows from 509 pages: Maintenance Service 16, Extended Warranty 14, O&amp;M Deliverable 11, Quantity Not Specified 10, Training 9, Spare Part 9, Attic Stock 5, Special Tool 2</t>
+          <t>79 candidate rows from 509 pages: Maintenance Service 16, Extended Warranty 14, Quantity Not Specified 13, O&amp;M Deliverable 11, Training 9, Spare Part 9, Attic Stock 5, Special Tool 2</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6550,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -6487,7 +6570,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -6507,7 +6590,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -6527,7 +6610,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -6547,7 +6630,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -6567,7 +6650,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -6587,11 +6670,11 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
@@ -6607,11 +6690,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6710,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -6647,7 +6730,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -6667,7 +6750,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -6687,7 +6770,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -6707,7 +6790,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -6727,7 +6810,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -6747,7 +6830,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -6767,7 +6850,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -6787,7 +6870,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -6807,7 +6890,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -6827,11 +6910,11 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
@@ -6847,11 +6930,11 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6950,7 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -6887,7 +6970,7 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -6907,7 +6990,7 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -6923,27 +7006,29 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>70</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>31 labor items; 8 computed from spec (48 h stated), 23 need estimator input</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>8 Div 23/26</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -6953,7 +7038,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>32 labor items; 8 computed from spec (48 h stated), 24 need estimator input</t>
+          <t>R16 26 28 18 ENCLOSED SWITCHES: calls for maintenance materials but lists none - RFI</t>
         </is>
       </c>
     </row>
@@ -6965,7 +7050,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -6975,7 +7060,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>R16 26 28 18 ENCLOSED SWITCHES: calls for maintenance materials but lists none - RFI</t>
+          <t>R16 Division 23 HVAC: 21 sections, 12 with requirements, 0 flagged CHECK</t>
         </is>
       </c>
     </row>
@@ -6997,14 +7082,14 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>R16 Division 23 HVAC: 21 sections, 12 with requirements, 0 flagged CHECK</t>
+          <t>R16 Division 26 Electrical: 12 sections, 2 with requirements, 1 flagged CHECK</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8 Div 23/26</t>
+          <t>4 Delivery</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -7019,29 +7104,27 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>R16 Division 26 Electrical: 12 sections, 2 with requirements, 1 flagged CHECK</t>
+          <t>R12 file re-opened and matches verified data (78 rows)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4 Delivery</t>
+          <t>7 Language</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>33</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>R12 file re-opened and matches verified data (75 rows)</t>
+          <t>R15 quote has no common English words - check source</t>
         </is>
       </c>
     </row>
@@ -7053,22 +7136,24 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>30</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>R15 quote has no common English words - check source</t>
+          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>7 Language</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7083,29 +7168,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Extraction and checks took 17 seconds</t>
+          <t>Extraction and checks took 16 seconds</t>
         </is>
       </c>
     </row>

--- a/spectakeoff/RCCD_Closeout_Schedule.xlsx
+++ b/spectakeoff/RCCD_Closeout_Schedule.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Closeout Schedule'!$A$2:$N$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source: RCCD.pdf (509 pages) - 78 requirements. Every quote verified word-for-word against the cited page.</t>
+          <t>Source: RCCD.pdf (509 pages) - 82 requirements. Every quote verified word-for-word against the cited page.</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>01 70 00</t>
+          <t>01 60 00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
+          <t>PRODUCT REQUIREMENTS</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -880,18 +880,18 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>copy of site drawing signed by the Land Surveyor, that the elevations and locations of the work are in complia</t>
+          <t>extra materials, spare parts, tools, and software of types and in quantities specified in individual specifica</t>
         </is>
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Submit a copy of site drawing signed by the Land Surveyor, that the elevations and locations of the work are in compliance with Contract Documents.</t>
+          <t>Furnish extra materials, spare parts, tools, and software of types and in quantities specified in individual specification sections.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>01 70 00</t>
+          <t>01 60 00</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
+          <t>PRODUCT REQUIREMENTS</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -922,18 +922,18 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>surveys and survey logs for the project record</t>
+          <t>Deliver to Project site; obtain receipt prior to final payment</t>
         </is>
       </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Submit surveys and survey logs for the project record.</t>
+          <t>Deliver to Project site; obtain receipt prior to final payment.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -964,18 +964,18 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>written report that equipment or system has been properly installed and is functioning correctly</t>
+          <t>copy of site drawing signed by the Land Surveyor, that the elevations and locations of the work are in complia</t>
         </is>
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Submit a written report that equipment or system has been properly installed and is functioning correctly.</t>
+          <t>Submit a copy of site drawing signed by the Land Surveyor, that the elevations and locations of the work are in compliance with Contract Documents.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -989,50 +989,46 @@
       <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Quantity Not Specified</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
-        <v>244</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>surveys and survey logs for the project record</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Submit surveys and survey logs for the project record.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1047,33 +1043,23 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>8 hours minimum of demonstration and training</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>written report that equipment or system has been properly installed and is functioning correctly</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="n">
         <v>244</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Provide 8 hours minimum of demonstration and training.</t>
+          <t>Submit a written report that equipment or system has been properly installed and is functioning correctly.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1087,52 +1073,50 @@
       <c r="N13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>bound hardcopies - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1147,29 +1131,33 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>archival-grade (gold foil) DVDs - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
+          <t>8 hours minimum of demonstration and training</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
+          <t>Provide 8 hours minimum of demonstration and training.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1195,23 +1183,29 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>written certification that Contract Documents have been reviewed, work has been inspected, and that work is co</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>bound hardcopies - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="n">
         <v>245</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Submit written certification that Contract Documents have been reviewed, work has been inspected, and that work is complete in accordance with Contract Documents and ready for Architect's review.</t>
+          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1225,97 +1219,83 @@
       <c r="N16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>01 70 00</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Period</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>from the Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="n">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>archival-grade (gold foil) DVDs - operation and maintenance manuals for all installed equipment and devices, as-built drawin</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Period: As indicated in specification sections or, if not indicated, not less than one year from the Date of Substantial Completion or the length of the specified warranty, whichever is longer.</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Provide operation and maintenance manuals for all installed equipment and devices, as-built drawings (PDF), and all inspection certificates as two (2) bound hardcopies and two (2) archival-grade (gold foil) DVDs.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>01 78 00</t>
+          <t>01 70 00</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CLOSEOUT SUBMITTALS</t>
+          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>O&amp;M Deliverable</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>two sets of revised final documents in final form within 10 days after final inspection</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
+          <t>written certification that Contract Documents have been reviewed, work has been inspected, and that work is co</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Submit two sets of revised final documents in final form within 10 days after final inspection.</t>
+          <t>Submit written certification that Contract Documents have been reviewed, work has been inspected, and that work is complete in accordance with Contract Documents and ready for Architect's review.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1329,52 +1309,60 @@
       <c r="N18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>01 78 00</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>CLOSEOUT SUBMITTALS</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>253</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>01 70 00</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>EXECUTION AND CLOSEOUT REQUIREMENTS</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Period</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>from the Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Period: As indicated in specification sections or, if not indicated, not less than one year from the Date of Substantial Completion or the length of the specified warranty, whichever is longer.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1394,11 +1382,11 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+          <t>two sets of revised final documents in final form within 10 days after final inspection</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1407,11 +1395,11 @@
       </c>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+          <t>Submit two sets of revised final documents in final form within 10 days after final inspection.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1442,7 +1430,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, withi</t>
+          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -1455,11 +1443,11 @@
       </c>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Obtain warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, within 10 days after completion of the applicable item of work.</t>
+          <t>Two DVDs with All Project Record Submittals (Gold-Foil, Archival Grade DVDs)</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1473,116 +1461,100 @@
       <c r="N21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>01 78 00</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEOUT SUBMITTALS</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>O&amp;M Deliverable</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Training Manuals</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Maintain on site one set of the following record documents; record actual revisions to the Work:</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>01 78 00</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEOUT SUBMITTALS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, withi</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>for each attendee</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Training Manuals: Provide training manual for each attendee; allow for minimum of two attendees per training session.</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>01 79 00</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>DEMONSTRATION AND TRAINING</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>O&amp;M Deliverable</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>one extra copy of each training manual to be included with operation and maintenance data</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>of each training manual to be included with operation and maintenance data</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Provide one extra copy of each training manual to be included with operation and maintenance data.</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Obtain warranties and bonds, executed in duplicate by responsible Subcontractors, suppliers, and manufacturers, within 10 days after completion of the applicable item of work.</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1597,23 +1569,33 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>O&amp;M Deliverable</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
+          <t>Training Manuals</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>for each attendee</t>
+        </is>
+      </c>
       <c r="H24" s="4" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
+          <t>Training Manuals: Provide training manual for each attendee; allow for minimum of two attendees per training session.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1623,7 +1605,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L24" s="4" t="n"/>
@@ -1631,141 +1613,147 @@
       <c r="N24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>01 79 00</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>8 hours of training</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="n">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>O&amp;M Deliverable</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>one extra copy of each training manual to be included with operation and maintenance data</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>of each training manual to be included with operation and maintenance data</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>257</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Provide one extra copy of each training manual to be included with operation and maintenance data.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>01 79 00</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>DEMONSTRATION AND TRAINING</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six month</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
         <v>258</v>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum 8 hours of training.</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>03 30 00</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>CAST IN PLACE CONCRETE</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA)</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA): Provide warranty to cover the cost of flooring failures due to moisture migration from slabs for ten years.</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>For equipment or systems requiring seasonal operation, perform demonstration for other season within six months.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>03 30 00</t>
+          <t>01 79 00</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CAST IN PLACE CONCRETE</t>
+          <t>DEMONSTRATION AND TRAINING</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Moisture Emission Reducing Curing and Sealing Compound</t>
+          <t>8 hours of training</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H27" s="3" t="n">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Moisture Emission Reducing Curing and Sealing Compound: Provide warranty to cost of flooring delamination failures for 10 years.</t>
+          <t>Provide minimum 8 hours of training.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1781,39 +1769,39 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>09 51 00</t>
+          <t>03 30 00</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ACOUSTICAL CEILINGS</t>
+          <t>CAST IN PLACE CONCRETE</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project</t>
+          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA)</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="n">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Provide 100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project.</t>
+          <t>Slabs with Moisture Vapor Reducing Admixture (MVRA): Provide warranty to cover the cost of flooring failures due to moisture migration from slabs for ten years.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1829,39 +1817,39 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>09 51 00</t>
+          <t>03 30 00</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ACOUSTICAL CEILINGS</t>
+          <t>CAST IN PLACE CONCRETE</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1 box of Type A2 acoustical unit, for Owner's use in maintenance of project</t>
+          <t>Moisture Emission Reducing Curing and Sealing Compound</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="n">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Provide 1 box of Type A2 acoustical unit, for Owner's use in maintenance of project.</t>
+          <t>Moisture Emission Reducing Curing and Sealing Compound: Provide warranty to cost of flooring delamination failures for 10 years.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1875,97 +1863,89 @@
       <c r="N29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>09 90 00</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>PAINTS AND COATINGS</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>09 51 00</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>ACOUSTICAL CEILINGS</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Attic Stock</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>1 gallon of each color; store where directed</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>GAL</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>of each color</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>296</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Supply 1 gallon of each color; store where directed.</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Provide 100 SF of Type A1 acoustical unit, for Owner's use in maintenance of project.</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>23 05 13</t>
+          <t>09 51 00</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MOTOR REQUIREMENTS FOR HVAC AND PLUMBING EQUIPMENT</t>
+          <t>ACOUSTICAL CEILINGS</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Attic Stock</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>five year manufacturer warranty for motors larger than 20 horsepower</t>
+          <t>1 box of Type A2 acoustical unit, for Owner's use in maintenance of project</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Provide five year manufacturer warranty for motors larger than 20 horsepower.</t>
+          <t>Provide 1 box of Type A2 acoustical unit, for Owner's use in maintenance of project.</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1981,43 +1961,43 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>23 05 16</t>
+          <t>09 90 00</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>EXPANSION FITTINGS AND LOOPS FOR HVAC PIPING</t>
+          <t>PAINTS AND COATINGS</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Attic Stock</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>two sets of packing for each packed expansion joint</t>
+          <t>1 gallon of each color; store where directed</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>GAL</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>for each packed expansion joint</t>
+          <t>of each color</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Supply two sets of packing for each packed expansion joint.</t>
+          <t>Supply 1 gallon of each color; store where directed.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2037,12 +2017,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>23 05 93</t>
+          <t>09 90 00</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>TESTING, ADJUSTING, AND BALANCING FOR HVAC</t>
+          <t>PAINTS AND COATINGS</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2052,18 +2032,18 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>final copies for Architect and for inclusion in operating and maintenance manuals</t>
+          <t>Label each container with color, type, texture, and room locations in addition to the manufacturer's label</t>
         </is>
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="n">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Provide final copies for Architect and for inclusion in operating and maintenance manuals.</t>
+          <t>Label each container with color, type, texture, and room locations in addition to the manufacturer's label.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2077,145 +2057,139 @@
       <c r="N33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>23 09 13</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>INSTRUMENTATION AND CONTROL DEVICES FOR HVAC</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>23 05 13</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>MOTOR REQUIREMENTS FOR HVAC AND PLUMBING EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>five year manufacturer warranty for motors larger than 20 horsepower</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Provide five year manufacturer warranty for motors larger than 20 horsepower.</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>23 05 16</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>EXPANSION FITTINGS AND LOOPS FOR HVAC PIPING</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>two sets of packing for each packed expansion joint</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>352</v>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Provide service and maintenance of control system for two years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>for each packed expansion joint</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Supply two sets of packing for each packed expansion joint.</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>23 09 23</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>defective Work within a five year period after Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="n">
-        <v>354</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>Correct defective Work within a five year period after Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 05 93</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+          <t>TESTING, ADJUSTING, AND BALANCING FOR HVAC</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>five year manufacturer's warranty for field programmable micro-processor based units</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
+          <t>final copies for Architect and for inclusion in operating and maintenance manuals</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="3" t="n">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Provide five year manufacturer's warranty for field programmable micro-processor based units.</t>
+          <t>Provide final copies for Architect and for inclusion in operating and maintenance manuals.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2231,12 +2205,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>23 09 23</t>
+          <t>23 09 13</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+          <t>INSTRUMENTATION AND CONTROL DEVICES FOR HVAC</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2246,11 +2220,11 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
+          <t>service and maintenance of control system for two years from Date of Substantial Completion</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
@@ -2263,11 +2237,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Provide service and maintenance of energy management and control systems for one years from Date of Substantial Completion.</t>
+          <t>Provide service and maintenance of control system for two years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2285,60 +2259,52 @@
       <c r="N37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>23 09 23</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>per year</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>defective Work within a five year period after Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="n">
         <v>354</v>
       </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Provide four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required, and submit written reports.</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Correct defective Work within a five year period after Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2353,33 +2319,29 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service</t>
+          <t>five year manufacturer's warranty for field programmable micro-processor based units</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service calls to inspect, calibrate, and adjust controls, and submit written reports.</t>
+          <t>Provide five year manufacturer's warranty for field programmable micro-processor based units.</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2405,29 +2367,33 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
+          <t>service and maintenance of energy management and control systems for one years from Date of Substantial Comple</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>DAY</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
       <c r="H40" s="4" t="n">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Provide service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day period.</t>
+          <t>Provide service and maintenance of energy management and control systems for one years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2437,7 +2403,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L40" s="4" t="n"/>
@@ -2445,153 +2411,149 @@
       <c r="N40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>23 09 23</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>minimum of 8 hours dedicated instructor time</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Provide four complete inspections per year, two in each season, to inspect, calibrate, and adjust controls as required, and submit written reports.</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>23 09 23</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>minimum</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>373</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Include a minimum of 8 hours dedicated instructor time.</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="H42" s="3" t="n">
+        <v>355</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Make minimum of 4 complete normal inspections of approximately 4 hours duration in addition to normal service calls to inspect, calibrate, and adjust controls, and submit written reports.</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>23 21 13</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>HYDRONIC PIPING</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Special Tool</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>for every ten plug valves minimum of one</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>385</v>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Operator: One plug valve wrench for every ten plug valves minimum of one.</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="n"/>
-      <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
+      <c r="N42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>23 21 23</t>
+          <t>23 09 23</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>HYDRONIC PUMPS</t>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Extra Pump Seals</t>
+          <t>service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day peri</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>for each type and size of pump</t>
-        </is>
-      </c>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="n">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Extra Pump Seals: One set for each type and size of pump.</t>
+          <t>Provide service engineer to instruct Owner's representative in operation of systems plant and equipment for 2 day period.</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2601,7 +2563,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
       <c r="L43" s="4" t="n"/>
@@ -2609,95 +2571,97 @@
       <c r="N43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>23 25 00</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>HVAC WATER TREATMENT</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>398</v>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Furnish service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>23 09 23</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT DIGITAL CONTROL SYSTEM FOR HVAC</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>minimum of 8 hours dedicated instructor time</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Include a minimum of 8 hours dedicated instructor time.</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 21 13</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>HVAC WATER TREATMENT</t>
+          <t>HYDRONIC PIPING</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Special Tool</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="inlineStr"/>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>monthly - count not stated in this sentence, estimator must compute it</t>
+          <t>for every ten plug valves minimum of one</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Provide monthly technical service visits to perform field inspections and make water analysis on site.</t>
+          <t>Operator: One plug valve wrench for every ten plug valves minimum of one.</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2707,7 +2671,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L45" s="4" t="n"/>
@@ -2717,39 +2681,43 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>23 25 00</t>
+          <t>23 21 23</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>HVAC WATER TREATMENT</t>
+          <t>HYDRONIC PUMPS</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>two copies of field service report after each visit</t>
+          <t>Extra Pump Seals</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr"/>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>for each type and size of pump</t>
+        </is>
+      </c>
       <c r="H46" s="4" t="n">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Submit two copies of field service report after each visit.</t>
+          <t>Extra Pump Seals: One set for each type and size of pump.</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2759,7 +2727,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L46" s="4" t="n"/>
@@ -2779,29 +2747,23 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing,</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
+          <t>Operation and Maintenance Data</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="3" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Include 2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, and operation of water treatment systems.</t>
+          <t>Operation and Maintenance Data: Include data on chemical feed pumps, agitators, and other equipment including spare parts lists, procedures, and treatment programs.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2815,46 +2777,60 @@
       <c r="N47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>sufficient chemicals for treatment and testing during warranty period</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="n">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>Supply sufficient chemicals for treatment and testing during warranty period.</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="N48" s="3" t="n"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Furnish service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2874,18 +2850,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>monthly technical service visits to perform field inspections and make water analysis on site</t>
         </is>
       </c>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>monthly - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
       <c r="H49" s="4" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of chemical treatment system.</t>
+          <t>Provide monthly technical service visits to perform field inspections and make water analysis on site.</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -2895,7 +2875,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.400) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L49" s="4" t="n"/>
@@ -2903,253 +2883,233 @@
       <c r="N49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>23 25 00</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>two copies of field service report after each visit</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Submit two copies of field service report after each visit.</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>23 25 00</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>HVAC WATER TREATMENT</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>two hours of instruction for two people</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing,</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="n">
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="n">
+        <v>398</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Include 2 hour training course for operating personnel, instructing them on installation, care, maintenance, testing, and operation of water treatment systems.</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>23 25 00</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>HVAC WATER TREATMENT</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>sufficient chemicals for treatment and testing during warranty period</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="n">
+        <v>398</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Supply sufficient chemicals for treatment and testing during warranty period.</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="n"/>
+      <c r="M52" s="3" t="n"/>
+      <c r="N52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>23 25 00</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>HVAC WATER TREATMENT</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="n">
         <v>399</v>
       </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum of two hours of instruction for two people.</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr"/>
-      <c r="L50" s="3" t="n"/>
-      <c r="M50" s="3" t="n"/>
-      <c r="N50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>23 25 00</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>HVAC WATER TREATMENT</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>Provide service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Training: Train Owner's personnel on operation and maintenance of chemical treatment system.</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>23 25 00</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>HVAC WATER TREATMENT</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>bi-monthly - count not stated in this sentence, estimator must compute it</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>Provide bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and make water analysis on site.</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>23 64 23</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>SCROLL WATER CHILLER</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Extra Refrigerant</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="n">
-        <v>414</v>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>Extra Refrigerant: One container.</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="N53" s="3" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>SCROLL WATER CHILLER</t>
+          <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Extra Lubricating Oil</t>
+          <t>two hours of instruction for two people</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H54" s="3" t="n">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Extra Lubricating Oil: One container.</t>
+          <t>Provide minimum of two hours of instruction for two people.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -3163,87 +3123,101 @@
       <c r="N54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>23 64 23</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>SCROLL WATER CHILLER</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>23 25 00</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>HVAC WATER TREATMENT</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of treatment systems for one year from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>414</v>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer's Warranty: Provide minimum Five year warranty to include coverage for materials and labor for compressor.</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="n"/>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="3" t="n"/>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Provide service and maintenance of treatment systems for one year from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>23 64 23</t>
+          <t>23 25 00</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>SCROLL WATER CHILLER</t>
+          <t>HVAC WATER TREATMENT</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
+          <t>bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and m</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>bi-monthly - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
       <c r="H56" s="4" t="n">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+          <t>Provide bi-monthly (every 2 months) technical service visits for the first 6 months to perform field inspections and make water analysis on site.</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3253,7 +3227,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R10 CONFLICT: visits for this section are stated differently elsewhere (p.398) - raise an RFI | R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L56" s="4" t="n"/>
@@ -3273,33 +3247,29 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>Extra Refrigerant</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="3" t="n">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum of two hours of training.</t>
+          <t>Extra Refrigerant: One container.</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -3313,97 +3283,93 @@
       <c r="N57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>23 64 23</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>418</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Extra Lubricating Oil</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Extra Lubricating Oil: One container.</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" s="3" t="n"/>
+      <c r="N58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
+          <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Extra Refrigerant</t>
+          <t>Manufacturer's Warranty</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H59" s="3" t="n">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Extra Refrigerant: One container.</t>
+          <t>Manufacturer's Warranty: Provide minimum Five year warranty to include coverage for materials and labor for compressor.</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -3417,72 +3383,70 @@
       <c r="N59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>23 64 26</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Extra Lubricating Oil</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>Extra Lubricating Oil: One container.</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr"/>
-      <c r="L60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>23 64 23</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>SCROLL WATER CHILLER</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Quantity Not Specified</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>23 64 26</t>
+          <t>23 64 23</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
+          <t>SCROLL WATER CHILLER</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Manufacturer's Warranty</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3490,16 +3454,20 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
       <c r="H61" s="3" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Manufacturer's Warranty: 2 year parts and labor warranty for entire system.</t>
+          <t>Provide minimum of two hours of training.</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -3513,102 +3481,108 @@
       <c r="N61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>23 64 23</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>SCROLL WATER CHILLER</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
+      <c r="N62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>23 64 26</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>five year warranty to include coverage for materials only for compressor</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="n">
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Spare Part</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Extra Refrigerant</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="n">
         <v>420</v>
       </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>Provide minimum five year warranty to include coverage for materials only for compressor.</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Extra Refrigerant: One container.</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr"/>
-      <c r="L62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>23 64 26</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>ROTARY-SCREW WATER CHILLERS</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Quantity Not Specified</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="n">
-        <v>424</v>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="n"/>
-      <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="n"/>
+      <c r="M63" s="3" t="n"/>
+      <c r="N63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3623,33 +3597,29 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>two hours of training</t>
+          <t>Extra Lubricating Oil</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
       <c r="H64" s="3" t="n">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum of two hours of training.</t>
+          <t>Extra Lubricating Oil: One container.</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -3663,157 +3633,135 @@
       <c r="N64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>23 64 26</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="n">
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>from Date of Substantial Completion</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>424</v>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer's Warranty: 2 year parts and labor warranty for entire system.</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="n"/>
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>23 73 13</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Spare Part</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Extra Fan Belts</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>for each unit</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>426</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>Extra Fan Belts: One set for each unit.</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="n"/>
-      <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>23 64 26</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>five year warranty to include coverage for materials only for compressor</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Provide minimum five year warranty to include coverage for materials only for compressor.</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="n"/>
+      <c r="M66" s="3" t="n"/>
+      <c r="N66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>23 73 13</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Spare Part</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Extra Filters</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>for each unit</t>
-        </is>
-      </c>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Extra Filters: One set for each unit.</t>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -3823,7 +3771,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L67" s="4" t="n"/>
@@ -3833,22 +3781,22 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>23 73 13</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or wo</t>
+          <t>two hours of training</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -3856,7 +3804,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>YR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -3865,11 +3813,11 @@
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Provide minimum two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or workmanship.</t>
+          <t>Provide minimum of two hours of training.</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -3885,33 +3833,43 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>23 73 13</t>
+          <t>23 64 26</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+          <t>ROTARY-SCREW WATER CHILLERS</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
+          <t>separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
       <c r="H69" s="4" t="n">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
+          <t>Provide a separate maintenance contract for the service and maintenance of chiller for 2 years from Date of Substantial Completion.</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -3941,12 +3899,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>one day of training</t>
+          <t>Extra Fan Belts</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -3954,20 +3912,20 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>minimum</t>
+          <t>for each unit</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Provide minimum of one day of training.</t>
+          <t>Extra Fan Belts: One set for each unit.</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -3977,7 +3935,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L70" s="4" t="n"/>
@@ -3997,33 +3955,33 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Spare Part</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
+          <t>Extra Filters</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>YR</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>from Date of Substantial Completion</t>
+          <t>for each unit</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Provide service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion.</t>
+          <t>Extra Filters: One set for each unit.</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4033,7 +3991,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
       <c r="L71" s="4" t="n"/>
@@ -4041,60 +3999,56 @@
       <c r="N71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>23 73 13</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance Service</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>three month interval - count not stated in this sentence, estimator must compute it</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>432</v>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>Provide routine maintenance service with a three month interval as maximum time period between calls.</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or wo</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>426</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Provide minimum two year manufacturer parts and labor warranty covering repair or replacement due to defective materials or workmanship.</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -4109,33 +4063,23 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>minimum</t>
-        </is>
-      </c>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
+          <t>Training: Train Owner's personnel on operation and maintenance of system.</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -4165,12 +4109,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
+          <t>one day of training</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -4178,7 +4122,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -4187,11 +4131,11 @@
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
+          <t>Provide minimum of one day of training.</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -4201,7 +4145,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
       <c r="L74" s="4" t="n"/>
@@ -4209,172 +4153,196 @@
       <c r="N74" s="4" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>23 81 01</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>five year manufacturers warranty for all motors</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>YR</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>Provide five year manufacturers warranty for all motors.</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>from Date of Substantial Completion</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Provide service and maintenance of packaged roof top units for [2] years from Date of Substantial Completion.</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>23 81 01</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Extended Warranty</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>one year parts and labor warranty for enitre unit, from substitute and completion</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>YR</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>Provide one year parts and labor warranty for enitre unit, from substitute and completion.</t>
-        </is>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr"/>
-      <c r="L76" s="3" t="n"/>
-      <c r="M76" s="3" t="n"/>
-      <c r="N76" s="3" t="n"/>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>routine maintenance service with a three month interval as maximum time period between calls</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>three month interval - count not stated in this sentence, estimator must compute it</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Provide routine maintenance service with a three month interval as maximum time period between calls.</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>23 81 01</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>TERMINAL HEAT TRANSFER UNITS</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Attic Stock</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>one (1) set of filters, with a final change immediately prior to occupancy</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>Provide one (1) set of filters, with a final change immediately prior to occupancy.</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr"/>
-      <c r="L77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
-      <c r="N77" s="3" t="n"/>
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>23 73 13</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Service</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>filter replacements - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>433</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
+      <c r="N77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>26 27 26</t>
+          <t>23 73 13</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>WIRING DEVICES</t>
+          <t>MODULAR CENTRAL-STATION AIR HANDLING UNITS</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Attic Stock</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>two of each style, size, and finish wall plate</t>
+          <t>fan belt replacement - maintenance items as outlined in manufacturer's operating and maintenance data, including</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
@@ -4383,15 +4351,15 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>of each style</t>
+          <t>minimum</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>479</v>
+        <v>433</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Furnish two of each style, size, and finish wall plate.</t>
+          <t>Include maintenance items as outlined in manufacturer's operating and maintenance data, including minimum of four (4) filter replacements, minimum of one fan belt replacement, and controls check-out, adjustments, and recalibration.</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -4401,7 +4369,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
       <c r="L78" s="4" t="n"/>
@@ -4411,39 +4379,39 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26 28 13</t>
+          <t>23 81 01</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>FUSES</t>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Special Tool</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>two fuse pullers</t>
+          <t>five year manufacturers warranty for all motors</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr"/>
       <c r="H79" s="3" t="n">
-        <v>483</v>
+        <v>435</v>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Furnish two fuse pullers.</t>
+          <t>Provide five year manufacturers warranty for all motors.</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -4457,63 +4425,263 @@
       <c r="N79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>23 81 01</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Extended Warranty</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>one year parts and labor warranty for enitre unit, from substitute and completion</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>YR</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Provide one year parts and labor warranty for enitre unit, from substitute and completion.</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="n"/>
+      <c r="M80" s="3" t="n"/>
+      <c r="N80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>23 81 01</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>TERMINAL HEAT TRANSFER UNITS</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>one (1) set of filters, with a final change immediately prior to occupancy</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Provide one (1) set of filters, with a final change immediately prior to occupancy.</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr"/>
+      <c r="L81" s="3" t="n"/>
+      <c r="M81" s="3" t="n"/>
+      <c r="N81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>26 27 26</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>WIRING DEVICES</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Attic Stock</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>two of each style, size, and finish wall plate</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>of each style</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>479</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Furnish two of each style, size, and finish wall plate.</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>26 28 13</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>FUSES</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Special Tool</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>two fuse pullers</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="n">
+        <v>483</v>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Furnish two fuse pullers.</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="n"/>
+      <c r="M83" s="3" t="n"/>
+      <c r="N83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>26 28 13</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>FUSES</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Spare Part</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>three of each size and type fuse installed</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E84" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>of each size and type fuse installed</t>
         </is>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <v>483</v>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>Furnish three of each size and type fuse installed.</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>R8 quantity is per unit/size/type - total needs the count from drawings/equipment schedules</t>
         </is>
       </c>
-      <c r="L80" s="4" t="n"/>
-      <c r="M80" s="4" t="n"/>
-      <c r="N80" s="4" t="n"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N80"/>
+  <autoFilter ref="A2:N84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4546,31 +4714,31 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maintenance Service</t>
+          <t>Quantity Not Specified</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Extended Warranty</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Quantity Not Specified</t>
+          <t>Extended Warranty</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -4630,7 +4798,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4707,7 +4875,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -4746,7 +4914,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -4787,7 +4955,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4826,7 +4994,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -4865,7 +5033,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -4906,7 +5074,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -4945,7 +5113,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -4984,7 +5152,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -5023,7 +5191,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -5064,7 +5232,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -5103,7 +5271,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -5144,7 +5312,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -5183,7 +5351,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -5222,7 +5390,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -5261,7 +5429,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -5302,7 +5470,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -5341,7 +5509,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -5382,7 +5550,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -5421,7 +5589,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -5460,7 +5628,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -5499,7 +5667,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -5540,7 +5708,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -5579,7 +5747,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -5618,7 +5786,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -5659,7 +5827,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -5698,7 +5866,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -5737,7 +5905,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -5776,7 +5944,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -5815,7 +5983,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -5854,7 +6022,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -5893,7 +6061,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -5941,7 +6109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5984,7 +6152,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -6004,7 +6172,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -6024,7 +6192,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -6044,7 +6212,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -6064,7 +6232,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -6084,7 +6252,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -6104,7 +6272,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -6124,7 +6292,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -6144,7 +6312,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -6164,7 +6332,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -6184,11 +6352,11 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>R6 duplicate of row 44</t>
+          <t>R6 duplicate of row 48</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6372,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -6224,7 +6392,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -6244,7 +6412,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -6336,7 +6504,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>R11 page 235: closeout keywords but no row - review manually</t>
+          <t>R11 page 259: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6526,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>R11 page 259: closeout keywords but no row - review manually</t>
+          <t>R11 page 348: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6548,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>R11 page 348: closeout keywords but no row - review manually</t>
+          <t>R11 page 381: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6570,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>R11 page 381: closeout keywords but no row - review manually</t>
+          <t>R11 page 469: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6592,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>R11 page 397: closeout keywords but no row - review manually</t>
+          <t>R11 page 488: closeout keywords but no row - review manually</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6604,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -6446,7 +6614,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>R11 page 469: closeout keywords but no row - review manually</t>
+          <t>48 intentionally blank pages skipped</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6626,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -6468,14 +6636,14 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>R11 page 488: closeout keywords but no row - review manually</t>
+          <t>83 candidate rows from 509 pages: Quantity Not Specified 17, Maintenance Service 16, Extended Warranty 14, O&amp;M Deliverable 11, Training 9, Spare Part 9, Attic Stock 5, Special Tool 2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2 Quality</t>
+          <t>6 Drawings</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6490,51 +6658,47 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>48 intentionally blank pages skipped</t>
+          <t>0 per-unit rows totalled from drawings/counts, 10 still need a count</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2 Quality</t>
+          <t>3 Labor</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>79 candidate rows from 509 pages: Maintenance Service 16, Extended Warranty 14, Quantity Not Specified 13, O&amp;M Deliverable 11, Training 9, Spare Part 9, Attic Stock 5, Special Tool 2</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6 Drawings</t>
+          <t>3 Labor</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>0 per-unit rows totalled from drawings/counts, 10 still need a count</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6714,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -6570,7 +6734,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -6590,7 +6754,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -6610,7 +6774,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -6630,11 +6794,11 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6814,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -6670,11 +6834,11 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 2 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6854,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -6710,7 +6874,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -6730,7 +6894,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -6750,7 +6914,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -6770,7 +6934,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -6790,7 +6954,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -6810,7 +6974,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -6830,7 +6994,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -6850,7 +7014,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -6870,11 +7034,11 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
         </is>
       </c>
     </row>
@@ -6890,7 +7054,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -6910,11 +7074,11 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: 1 day(s) stated - hours per day not stated in spec</t>
+          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
         </is>
       </c>
     </row>
@@ -6930,7 +7094,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -6950,7 +7114,7 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -6966,22 +7130,24 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>72</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>31 labor items; 8 computed from spec (48 h stated), 23 need estimator input</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>8 Div 23/26</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -6989,19 +7155,21 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n">
-        <v>73</v>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>R9 labor hours not stated: spec states the obligation but not the hours - estimator must price it</t>
+          <t>R16 26 28 18 ENCLOSED SWITCHES: calls for maintenance materials but lists none - RFI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3 Labor</t>
+          <t>8 Div 23/26</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -7016,7 +7184,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>31 labor items; 8 computed from spec (48 h stated), 23 need estimator input</t>
+          <t>R16 Division 23 HVAC: 21 sections, 12 with requirements, 0 flagged CHECK</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7196,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -7038,14 +7206,14 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>R16 26 28 18 ENCLOSED SWITCHES: calls for maintenance materials but lists none - RFI</t>
+          <t>R16 Division 26 Electrical: 12 sections, 2 with requirements, 1 flagged CHECK</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8 Div 23/26</t>
+          <t>4 Delivery</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -7060,36 +7228,34 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>R16 Division 23 HVAC: 21 sections, 12 with requirements, 0 flagged CHECK</t>
+          <t>R12 file re-opened and matches verified data (82 rows)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8 Div 23/26</t>
+          <t>7 Language</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>36</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>R16 Division 26 Electrical: 12 sections, 2 with requirements, 1 flagged CHECK</t>
+          <t>R15 quote has no common English words - check source</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4 Delivery</t>
+          <t>7 Language</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -7104,69 +7270,27 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>R12 file re-opened and matches verified data (78 rows)</t>
+          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7 Language</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>33</v>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>R15 quote has no common English words - check source</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>7 Language</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>R15 all sheets, headers and cells are English; quotes are original spec text</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Extraction and checks took 16 seconds</t>
         </is>
@@ -7668,11 +7792,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>OK - 9 requirement row(s)</t>
+          <t>OK - 10 requirement row(s)</t>
         </is>
       </c>
     </row>
